--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3545-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3545-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDE04936-90E6-45F4-9A19-669B348118AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30A10813-BE99-465B-B6A4-0E359E6B17E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{F5E67664-5EC7-4BD8-9298-B3FC2805DEE6}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{7C2928F2-C3A1-49B8-83B2-C90C1F9A2A19}"/>
   </bookViews>
   <sheets>
     <sheet name="3545-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1445,23 +1445,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FFD9A9F-F613-4B61-AC3D-C4126BBB06F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A51B013-B3BA-4812-AF47-8BF1D69D666F}">
   <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1489,7 +1489,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1519,7 +1519,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1615,7 +1615,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="40">
         <v>2024</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="38">
         <v>2023</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2022</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="38">
         <v>2021</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="40">
         <v>2020</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>26</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="38">
         <v>2019</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>2018</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2017</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2016</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="38">
         <v>2015</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2014</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2013</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2012</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2011</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2010</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2009</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2008</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2007</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40" t="s">
         <v>33</v>
       </c>
